--- a/data-manipulation-scripts/sheets-cleanup/sheets/JUNTA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/JUNTA EMBREAGEM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -28,136 +28,136 @@
     <t>7899641806637</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS YBR125/ CRUX YD100 2011 A 2017</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS YBR125/ CRUX YD100 2011 A 2017</t>
   </si>
   <si>
     <t>7899641814700</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS CG TITAN FAN150 2004/ CRF 150F 2012/ BROS NXR150 2006/ CG125 2009</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS CG TITAN FAN150 2004/ CRF 150F 2012/ BROS NXR150 2006/ CG125 2009</t>
   </si>
   <si>
     <t>7899641801953</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS CBX250 TWISTER/ TORNADO XR250/ CB300/ XRE300</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS CBX250 TWISTER/ TORNADO XR250/ CB300/ XRE300</t>
   </si>
   <si>
     <t>7899641801434</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS CG125 2000/ TITAN 2000 KS/ BROS NXR150 2002 A 2005/ NXR125 2003 A 2005</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS CG125 2000/ TITAN 2000 KS/ BROS NXR150 2002 A 2005/ NXR125 2003 A 2005</t>
   </si>
   <si>
     <t>7899641815325</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS YS-250 FAZER</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS YS-250 FAZER</t>
   </si>
   <si>
     <t>7899641815349</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS XT660R</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS XT660R</t>
   </si>
   <si>
     <t>7899641849740</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMOTORS BROS NXR160/ TITAN FAN CG160</t>
+    <t>JUNTA EMBREAGEM VEDAMOTORS BROS NXR160/ TITAN FAN CG160</t>
+  </si>
+  <si>
+    <t>7899641849757</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VEDAMOTORS BROS NXR160 2016/ CG FAN TITAN160 2016/ XRE190 2016</t>
+  </si>
+  <si>
+    <t>7899641816025</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VEDAMOTORS SUSUKI YES125 2005 A 2012/ INTRUDER125 2002/ KATANA 1996 A 2002</t>
+  </si>
+  <si>
+    <t>7899641815363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNTA EMBREAGEM VEDAMOTORS XT660R </t>
+  </si>
+  <si>
+    <t>7895443560234</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VALFLEX XRE190</t>
+  </si>
+  <si>
+    <t>7899641837211</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VEDAMOTORS FAZER YS150 2014/ FACTOR125I 2017</t>
+  </si>
+  <si>
+    <t>7895442562536</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VALFLEX BROS NXR150 2012 A 2015/ CG TITAN FAN125-150 2009 A 2022 56253</t>
+  </si>
+  <si>
+    <t>6942234802873</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM BRAVIC POP110/ BIZ110 2016 A 2018 BMA4812</t>
+  </si>
+  <si>
+    <t>7895443564331</t>
+  </si>
+  <si>
+    <t>JUNTA EMBREAGEM VALFLEX BROS NXR160 2015 A 2022 56433</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>7899641849757</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VEDAMOTORS BROS NXR160 2016/ CG FAN TITAN160 2016/ XRE190 2016</t>
-  </si>
-  <si>
-    <t>7899641816025</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VEDAMOTORS SUSUKI YES125 2005 A 2012/ INTRUDER125 2002/ KATANA 1996 A 2002</t>
-  </si>
-  <si>
-    <t>7899641815363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTA EMB VEDAMOTORS XT660R </t>
-  </si>
-  <si>
-    <t>7895443560234</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VALFLEX XRE190</t>
-  </si>
-  <si>
-    <t>7899641837211</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VEDAMOTORS FAZER YS150 2014/ FACTOR125I 2017</t>
-  </si>
-  <si>
-    <t>7895442562536</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VALFLEX BROS NXR150 2012 A 2015/ CG TITAN FAN125-150 2009 A 2022 56253</t>
-  </si>
-  <si>
-    <t>6942234802873</t>
-  </si>
-  <si>
-    <t>JUNTA EMB BRAVIC POP110/ BIZ110 2016 A 2018 BMA4812</t>
-  </si>
-  <si>
-    <t>7895443564331</t>
-  </si>
-  <si>
-    <t>JUNTA EMB VALFLEX BROS NXR160 2015 A 2022 56433</t>
-  </si>
-  <si>
     <t>7895442569238</t>
   </si>
   <si>
-    <t>JUNTA EMB VALFLEX TWISTER CB250 2018 A 2022 56923</t>
+    <t>JUNTA EMBREAGEM VALFLEX TWISTER CB250 2018 A 2022 56923</t>
   </si>
   <si>
     <t>7895442569030</t>
   </si>
   <si>
-    <t>JUNTA EMB VALFLEX CBX250 TWISTER/ XR250 TORNADO 56903</t>
+    <t>JUNTA EMBREAGEM VALFLEX CBX250 TWISTER/ XR250 TORNADO 56903</t>
   </si>
   <si>
     <t>VS10003090123</t>
   </si>
   <si>
-    <t>JUNTA EMB VEDAMTORS XT660R</t>
+    <t>JUNTA EMBREAGEM VEDAMTORS XT660R</t>
   </si>
   <si>
     <t>7893986261564</t>
   </si>
   <si>
-    <t>JUNTA EMB PEÇA+ CB300/ TWISTER/ XRE300</t>
+    <t>JUNTA EMBREAGEM PEÇA+ CB300/ TWISTER/ XRE300</t>
   </si>
   <si>
     <t>2789946808821</t>
   </si>
   <si>
-    <t>JUNTA EMB MHX TWISTER CBX250 2001 A 2008/ TORNADO XR250 2001 A 2008/ CB300R 2009 A 2016</t>
+    <t>JUNTA EMBREAGEM MHX TWISTER CBX250 2001 A 2008/ TORNADO XR250 2001 A 2008/ CB300R 2009 A 2016</t>
   </si>
   <si>
     <t>27899468088833</t>
   </si>
   <si>
-    <t>JUNTA MAG MHX CB300R 2010 A 2016</t>
+    <t>JUNTA EMBREAGEM MHX CB300R 2010 A 2016</t>
   </si>
   <si>
     <t>7893986287434</t>
   </si>
   <si>
-    <t>JUNTA EMB PEÇA+ FAZER250/ LANDER XTZ250</t>
+    <t>JUNTA EMBREAGEM PEÇA+ FAZER250/ LANDER XTZ250</t>
   </si>
 </sst>
 </file>
@@ -209,10 +209,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -479,10 +479,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>10.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -513,10 +515,12 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>12.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -547,10 +551,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>9.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -578,13 +584,15 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
         <v>32.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -612,7 +620,7 @@
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7">
@@ -648,13 +656,15 @@
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -682,14 +692,14 @@
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="7">
         <v>2.0</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
+      <c r="D8" s="4">
+        <v>20.0</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -716,15 +726,17 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="C9" s="7">
         <v>1.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -750,15 +762,17 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="C10" s="7">
         <v>5.0</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -784,15 +798,17 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="C11" s="7">
         <v>1.0</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -818,15 +834,17 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="C12" s="7">
         <v>4.0</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -852,15 +870,17 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="C13" s="7">
         <v>1.0</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -886,15 +906,17 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="C14" s="7">
         <v>7.0</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -920,15 +942,17 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="C15" s="7">
         <v>5.0</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -954,19 +978,21 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C16" s="7">
         <v>4.0</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
@@ -992,13 +1018,15 @@
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C17" s="7">
         <v>3.0</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -1026,7 +1054,7 @@
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="7">
@@ -1062,13 +1090,15 @@
       <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="7">
         <v>1.0</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="4">
+        <v>17.0</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1096,7 +1126,7 @@
       <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="7">
@@ -1132,7 +1162,7 @@
       <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="7">
@@ -1168,7 +1198,7 @@
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="7">
@@ -1204,7 +1234,7 @@
       <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="7">
